--- a/AAII_Financials/Quarterly/AMX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>AMX</t>
   </si>
@@ -656,542 +656,554 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13796500</v>
+      </c>
+      <c r="E8" s="3">
         <v>13137900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13603000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12698500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12397000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11352800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11370900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11411000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11250600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12268300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11872300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11705900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11811300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11581000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11255900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11254200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12711900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12307000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>50245600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11906400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22629100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11244600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10603700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12854500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12038300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11965500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13059300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12478400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12096100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11882400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12751900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11159600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13776500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>13592300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>13646800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12629400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12900500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>13662200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>14301700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13259600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7582800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7350700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>-2237000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7142300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7060600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6544100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>-1284900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6470800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6217200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7100400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-2131200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6745400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6822700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6543800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6514700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6446400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7370700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7208400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29581500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7030900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13425500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6704900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6516200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7999200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7387000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7394700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8045300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7880200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7601800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7449100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8145100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7177200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8761700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8738800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8946900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8120800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>8143900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>8743100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>9511400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>8521100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6213700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5787100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15840000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5556200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5336400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4808600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12655800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4940300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5033400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5167800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14003600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4960500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4988600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5037100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4741300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4807900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5341200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5098600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20664100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4875500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9203700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4539700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4087600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4855300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4651200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4570700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5014100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4598300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4494400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4433300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4606700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3982400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5014700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4853500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4699900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4508600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4756600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4919100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4790200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4738500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1234,8 +1246,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1356,8 +1369,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,19 +1494,22 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>234600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1498,11 +1517,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>45700</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1510,11 +1529,11 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-114600</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1522,8 +1541,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1600,53 +1619,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2523500</v>
+      </c>
+      <c r="E15" s="3">
         <v>2439900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10042900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2382500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2390000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2262100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7876600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2143700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2058600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2403300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8978300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2202400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2238900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2138700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1722,8 +1744,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1763,252 +1788,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10831200</v>
+      </c>
+      <c r="E17" s="3">
         <v>10335600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11817000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9965900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9886700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9160200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9809300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8988300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8759400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9808700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10501300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9320200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9460600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9135100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8926900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8877600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10229100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9898500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40488600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9567700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18422400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9198200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8847300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10626200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10080800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10103600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10845200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10567300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10304600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10167600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10966000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9562600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11946800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>11952100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12169600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>12109300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>11288800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12091800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12934200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>11663500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2965300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2802300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1785900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2732700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2510200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2192600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1561600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2422700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2491100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2459600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1371000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2385700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2350700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2445900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2329000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2376600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2482800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2408400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9757000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2338700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4206700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2046400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1756400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2228300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1957500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1861900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2214200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1911100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1791500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1714800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1785900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1597000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1829700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1640200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1477100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>520200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1611700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1570400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1367400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1596100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2051,618 +2083,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-98900</v>
+      </c>
+      <c r="E20" s="3">
         <v>11500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-720900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-320000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>34400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>322200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>945100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1625100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>242000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-173700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1323500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-290600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-471900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-304000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-410900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1021400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1606100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-927200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1437700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1189300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-658900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-55800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3276600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>28800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-149200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-83200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>412500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-87400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>465600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1304200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>488400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1539900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-799300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-302700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1982600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1022900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-838800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5587700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5230700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12549800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5138600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5220200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4420300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9116000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3621300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2924700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4620900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10523000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3264600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4880200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5056500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4226400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4174400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4570300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5903600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17701900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3709100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8589300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2807700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5076700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3614300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3898900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>436000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4085100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3807900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3694600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4061300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3452300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3703700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2636400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4348700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2027800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1730200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3284700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5680800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2757600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>779200</v>
+      </c>
+      <c r="E22" s="3">
         <v>778500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>693000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>904400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>819900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>713200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>687900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>717400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>744000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>806300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>652400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>660200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>587100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>594900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>537800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>560200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>643400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>581300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2115800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>481100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1014000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>515700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>415800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>446700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>516900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>504200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>429200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>470500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>490500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>467100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>384700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>320900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>430100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>438700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>390200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>383500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>383000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>410400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>472200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>471600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2386900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2133300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1870400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2031600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2102400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1536300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>755100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>892200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>227400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1537000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1452600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>556100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2168000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2434300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1799400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1512500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1428600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2848500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6035100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>930400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3191400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>93000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2529900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1122700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1384800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1918900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1813700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1291400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1217800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1660200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1313700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1741700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>95400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1689900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-453000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-662600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>926000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3142600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-127700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>285700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>909200</v>
+      </c>
+      <c r="E24" s="3">
         <v>764900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>738400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>701300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>849800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>571800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>488400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>491300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>234200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>673500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>321300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>364700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>588200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>702700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>541400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>615500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>510200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>934900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1652900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>212200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1042300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>118600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>863400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>107100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>390200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-575200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>760000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>574100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>497300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>677400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>629800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>853300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>675700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>148100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-236600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>136800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1241700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>140900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>104900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2783,252 +2831,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1477600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1368400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1132100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1330300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1252600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>964500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>266700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>400900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>863400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1131400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>191500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1579800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1731600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1258100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>897000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>918400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1913700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4382200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>718300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2149100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1666500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1015500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>994500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1053700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>717400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>720500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>982700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>684000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>888400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>59300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1014200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-601100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-426000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>789200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1900900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-268600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>180900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1392500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1298100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1062800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1237600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1181600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>915100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>195500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>328200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-59800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>814300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1068400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>116500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1509000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1204000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>804200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>834600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1843400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4152900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>618200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2027300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1643600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>933800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>933100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1381000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1051600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>655000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>694700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>945800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>670600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>849900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-584200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-493800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>740300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1854400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-317100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3149,8 +3206,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,34 +3254,34 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-489400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>155200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-15100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>7148100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>274900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>405300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>175700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>230200</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3229,8 +3289,8 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3271,8 +3331,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3393,8 +3456,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3515,252 +3581,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>720900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>320000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-34400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-322200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-945100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1625100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-242000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>173700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1323500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>290600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>471900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>304000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>410900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1021400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1606100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>927200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1437700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1189300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>658900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>55800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3276600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>149200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>83200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-412500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>87400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-465600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1304200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-488400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1539900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>799300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>302700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1982600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1022900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>838800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1392500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1298100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1062800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1237600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1181600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>915100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>195500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>328200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-59800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>814300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1068400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>116500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1509000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>714500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>959400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>819500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1844400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11301000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>893200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2432600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>98700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1873800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>933800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>933100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1381000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1051600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>655000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>694700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>945800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>670600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>849900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-584200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-493800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>740300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1854400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-317100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3881,257 +3956,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1392500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1298100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1062800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1237600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1181600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>915100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>195500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>328200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-59800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>814300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1068400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>116500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1509000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>714500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>959400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>819500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1844400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11301000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>893200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2432600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>98700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1873800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>933800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>933100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1381000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1051600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>655000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>694700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>945800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>670600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>849900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-584200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-493800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>740300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1854400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-317100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4174,8 +4258,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4218,1106 +4303,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2907700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2857500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1941600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2712600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2420400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1726100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1759000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1268400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1712700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1649000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1573300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1623400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1883600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2091300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1756500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1477800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2101900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3322300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2271700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2005700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2180000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2825800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1803800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1776300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2526900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5235500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>979800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>805400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1576600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>828300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>987700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>738500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1095100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1057300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1255300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1317000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1080800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>618100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1232900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>973800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1417400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2295800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2356800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2721700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2863100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3067700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2241200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3301400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2948100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2669600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4362700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4381500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5245100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5313300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4608900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4751800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7108700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7665400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6912700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4127600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3926500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4201400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2743800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3631000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4037600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4552000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2706500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3202300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2689300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2759400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2476200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2370200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3244900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3038100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3057700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2843300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2609400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>2649100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>2961200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>3139700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14317200</v>
+      </c>
+      <c r="E43" s="3">
         <v>13265100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13477000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13460200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12624000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11459400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10678800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11926300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11944200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12818000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12295900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12546900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11930400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10911300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10513200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11342700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12480300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12641700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11981200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11817800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11218600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11261200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10514500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10179800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10456100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10722100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10220700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>10818600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10691600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10596500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9917600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8435500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10473200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>10748300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10067000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8899400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8538300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9012400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>10115500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9221400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1741800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1499600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1572300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1360100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1384800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1337600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1139800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1289300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1272600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1284600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1139900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1181000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1276900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1297000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1250600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1699000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2013700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1982800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1420400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2003800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1727900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1685400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1525600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1730400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1618100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1879100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2039500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2094000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1868600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2002600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1837900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1793500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2160200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1899300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2007200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1917600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1709900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1537100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1957900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2142800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1261300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1381900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>863500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1081500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1251200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1224900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1081200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>944100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1183000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1389600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>624800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>897200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1132600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1269400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>686300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>834400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1092600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1207400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1150100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>760200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>838700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>991000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1502700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>722100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>705800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>951800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>470100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>826100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>992300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1152900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>697500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1483600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2000200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2063200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1313200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1810100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2132700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1888000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2366400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21645500</v>
+      </c>
+      <c r="E46" s="3">
         <v>21299900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20280900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21336100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20543600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18815800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16974200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18729500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19060500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19810600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20121200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20630000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21468600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20882400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18815500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20105700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24797300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26819700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23736100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20715000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19891700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20964900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18090400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18039600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19344500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23340600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16416500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17746500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17818400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17339700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15916900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14821300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18973600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>18806200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17700400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>16787400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>15860300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>15949400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>18155400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>17844200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1359300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1263100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1244500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1154900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1092200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>953400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>844000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1896500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1915100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1910100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1732800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1752700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2008400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1899500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2068200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1582000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1753100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1861000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>586200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1131800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1113400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1037100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>483200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1185100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1313800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1511400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1600800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1178300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1460400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1490700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1383000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1526500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1472500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>699300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1118700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1107400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1302000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1314700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1831300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49710100</v>
+      </c>
+      <c r="E48" s="3">
         <v>49120900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49147200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46861100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46642200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45051000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43827200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44643000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44536400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47849800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43903000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42810800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43055800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>41288900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40606700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>41982800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49621100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>51160200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>48250800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45152100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43815900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>44103000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41426800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>37203500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>37169600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>38596800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>37579500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>36676600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>36407300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>36100900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>29184000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26613100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>33748900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>33762800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>34980500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>32227700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>31833800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>33850400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>37233200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>35207300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16676200</v>
+      </c>
+      <c r="E49" s="3">
         <v>16653700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16480500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16085200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16080400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15185500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14328700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15417100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15102200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15983200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15827500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15313200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14976000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14509500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14073200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14681000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16509600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16866500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16432900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>14930400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14661700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14793600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>13886300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>14161800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>14140600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>14098400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>13797800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>13147500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>13056800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>13049200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>12207300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11642600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>14650200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>14956900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>15257500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>14673600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>14236500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>14941100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16195600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>15821200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5438,8 +5551,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5560,130 +5676,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3854300</v>
+      </c>
+      <c r="E52" s="3">
         <v>3825800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3211200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3623500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3419100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3027900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2313500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2522800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2468000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2619200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2226700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2763100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2270600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2160600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8771800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8690400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9516400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9768500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10227200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8591100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8119300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8038900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7723100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7677800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7511400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7526000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6619900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6427400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6579400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7017400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6481300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6697600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8521100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8046700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8229100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>7359500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>6860900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>6958700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>7549800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>7161400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5804,130 +5926,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>103633800</v>
+      </c>
+      <c r="E54" s="3">
         <v>102305400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>99960900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>97747000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96245900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>91297700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>86091400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91197700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>91033800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>96610800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92523100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>91430400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>91739700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88320200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>84335300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>87041900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>102197500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>106476000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>99233100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>90520500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>87601900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>88937500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>81609900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>78267800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>79479900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>85073200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>76014500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>75176300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>75322200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>74997800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>65172600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>60989500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>77420400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>77045000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>76866900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>72166800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>69898900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>73001700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>80448700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>77865500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5970,8 +6098,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6014,740 +6143,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3199500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3106400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3731600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2909000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2820100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2921900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3140700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2848900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2764500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3477500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4140700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3468200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3339400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3480100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3608700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3314100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4085400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4418700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12127000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3950000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3786100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3373000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9390900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3971000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3857600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4444000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5625500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5135700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5055400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4898300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5399300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3993800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4678500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4062400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10999500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4611600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4629100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4428200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7051500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5666600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6852000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7950200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7104000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6502500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7626600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7792800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6703300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7617400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7418700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7738600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10963000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10300300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11635200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11225300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7032400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9505700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9429100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11214600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10151800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9861600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7935200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7702900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8695600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7363300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6043100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7977200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7694400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7973700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8998400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9086400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4388100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3146600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3020500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3345400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2676300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3099800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2972500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3598300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4386400</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>4203800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13985800</v>
+      </c>
+      <c r="E59" s="3">
         <v>12573400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11448000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10614300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10968100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10156900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9910100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9572900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10845400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11820400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11919400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10284300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11046000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10596800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14839200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16170900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19092600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19114300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9083800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16356900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15829000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15753800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7390600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13228500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13870600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13135400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12750500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12871100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13067600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11819300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11511900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11884000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15386300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14455800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7702000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13215200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>13507100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13257300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>13519300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>13331900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30333500</v>
+      </c>
+      <c r="E60" s="3">
         <v>29572800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27505700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26330500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27548600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26465500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23726600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25946000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26897800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29324600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31019100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30646300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32569000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31353100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25480300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28990700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32607000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34747700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31362600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30168400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27550300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26829700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>25477100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24562700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23771300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25556600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>26070300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25980600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>27121400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25804100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>21299300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19024500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>23085300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>21863600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>21377800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>20926500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>21108600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>21283900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>24957200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>23202300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32712700</v>
+      </c>
+      <c r="E61" s="3">
         <v>33399100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33948200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34489600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33125800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31815600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30764000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30994900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31009100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>32905800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26056400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26366900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24380800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24119600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26571400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25661500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30621900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30963900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28767700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28901400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29755800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32959300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28352200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32546300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35448900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>38589100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29265100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>29181100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28148400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28189000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24746700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>25887000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33785600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33220700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33418300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>30704200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>29149700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>29845300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>33197800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>33427800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1933300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1810500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1714000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1684500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1616700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1489700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1379100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1452500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1174000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>581400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>598500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>615800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>605800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>582000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9464000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9348900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12233400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12674200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12437000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13247300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13043800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13146800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11955400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9854100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9786300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9808400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9420000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8021300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7992700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8536300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7914700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7280900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>8886500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>8984200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>8590800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7628800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7448600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7779300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7902400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>8689700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6868,8 +7016,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6990,8 +7141,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7112,130 +7266,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78561300</v>
+      </c>
+      <c r="E66" s="3">
         <v>78106000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>76205500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72925700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72654900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69535400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65350600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>66838200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68181700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72840200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67579000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67050500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67463200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65634000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>64852600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>67315400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>79164000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>82245700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>76349900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>76040100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73805800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>76539500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>69030900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>69774300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>71654400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>76535600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>67186700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>65675100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>65625700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>64950200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>56235200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>54425500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>68498600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>66819900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>66824700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>62512300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>60788200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>62022300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>69355300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>68586500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7278,8 +7438,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7400,8 +7561,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7522,8 +7686,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7644,8 +7811,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7766,130 +7936,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32538300</v>
+      </c>
+      <c r="E72" s="3">
         <v>30354000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30965700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29402400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27486600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24498300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24823100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26503000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28255100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31666100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32275900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30649400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31186100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28257900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26345800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26497400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26897400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>26456900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>26292900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18601200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17617800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15598800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15805100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12553900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11240400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11408900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13522500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12739700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11561400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12175200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10371400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8678700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9361600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10518800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8848700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9134400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9340100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9646700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8020500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>8217400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8010,8 +8186,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8132,8 +8311,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8254,130 +8436,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21490000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20523000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20111400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21252800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20089100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18529600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17712600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21109500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19792600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20545000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21691400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21104700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20743200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19176400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19482700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19726500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23033500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24230300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22883300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14480400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13796100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12398000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12579000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8493500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7825600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8537600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8827900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9501100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9696500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10047600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8937400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6564000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8921800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10225100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10042200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9654500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9110800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10979400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11093400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9279000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8498,257 +8686,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1392500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1298100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1062800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1237600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1181600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>915100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>195500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>328200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-59800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>814300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1068400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>116500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1509000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>714500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>959400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>819500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1844400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11301000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>893200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2432600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>98700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1873800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>933800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>933100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1381000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1051600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>655000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>694700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>945800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>670600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>849900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-584200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-493800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>740300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1854400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-317100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8791,130 +8988,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2390000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2262100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1165500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2143700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2058600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2403300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1093800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2202400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2238900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2138700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1117000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1908300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2003000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1889200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2101700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2498400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2473700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9551100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2279200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4401700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2208100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2131000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2044900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1997300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1850700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1842200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2046000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1986300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1934000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1753800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1641100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2111000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2220100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2090600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2009300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1975700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2127800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2119900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2000300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9035,8 +9236,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9157,8 +9361,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9279,8 +9486,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9401,8 +9611,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9523,130 +9736,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4464000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2485000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4762100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4114100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3782900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1950400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3900200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3431100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3451700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1679200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5373700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4249700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3488000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1298800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4098700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3340300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3801800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1397100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15163000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4018300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7130600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2901800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4039200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4285200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3944600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1493700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4427000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3400500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3095400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>645900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4878800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2430700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3514300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1167800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4090900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2183600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3024800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1970700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4535500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2928500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9689,130 +9908,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1524200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1099800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2087900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1555800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1547100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-936100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1531300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1678900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1609700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1140100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2482300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1878900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1866700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1353000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-52802700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-39473700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36971400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28606200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-67185300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34490400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2840700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1289500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1664900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1344500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1237200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1085400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2097200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1543200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1645600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1251200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2567200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1435300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1118200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2172000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1465600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1109400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1432400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3144700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-2208500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9933,8 +10156,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10055,130 +10281,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1462000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-379200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2519700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1434900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1462600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1156400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1748000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1540500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1982400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1595000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3192100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2716400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2774700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-976600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2170700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>787200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3161600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1715800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4494100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1815100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3206100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1537500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2157900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1384600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1805100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1284200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2944300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1634300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1805500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1638500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2734200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1498500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1691500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1285500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2863100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1684800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3199300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2197300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10221,130 +10453,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>500</v>
+      </c>
+      <c r="E96" s="3">
         <v>400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>855100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>843200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>121900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>694100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>843900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>839500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>820800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>115200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1575000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1634400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-734700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-108700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-277800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-199400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-547900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-587500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-72100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-474200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-468400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-82900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-490100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-255300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-86500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-236900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-479500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10465,8 +10701,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10587,8 +10826,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10709,370 +10951,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2905000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1226400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2946700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2407600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1727700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-897700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1610200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2347400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1280000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2176500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1721100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1045100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1532000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4482700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1819600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1416300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10416700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2423100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3667800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-453200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1741000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3694800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4805900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3971000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1278300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2536900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-604400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>844900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1909700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1086800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1847600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-46600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1470300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-150900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1470100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-841300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1132800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2278200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E101" s="3">
         <v>36600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>127500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>27600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-27200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-104100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-43600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-70900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-84500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-80800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-38100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-34000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-76900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-82100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-40800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-41100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-91800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-90000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-33600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-34600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-43200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-142300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-38300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-42300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>110200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-20500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-60800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-26300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-33100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>59600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>9600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-25800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-40200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>55700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E102" s="3">
         <v>918600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-822200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>224100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>549600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>567000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-329300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>216900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>43900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-98900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-231300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-402700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>223300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>313900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-396000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1220400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1005800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>162200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-253500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>222100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>867900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-832500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2708600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4290700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>184000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-831400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>748300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-219400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>239500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-180900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-243800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-182900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>357400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>462800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-582800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>259100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1517100</v>
       </c>
     </row>
